--- a/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-bundle-admision-urgencia.xlsx
+++ b/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-bundle-admision-urgencia.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6348" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6348" uniqueCount="431">
   <si>
     <t>Property</t>
   </si>
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia/StructureDefinition/bundle-admision-urgencia</t>
+    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia-eventos/StructureDefinition/bundle-admision-urgencia</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T16:36:45-03:00</t>
+    <t>2026-09-24T11:47:41-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia/StructureDefinition/bundle-urgencia</t>
+    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia-eventos/StructureDefinition/bundle-urgencia</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -262,7 +262,7 @@
 </t>
   </si>
   <si>
-    <t>Contains a collection of resources</t>
+    <t>Bundle transaction de un evento de urgencia</t>
   </si>
   <si>
     <t>A container for a collection of resources.</t>
@@ -395,16 +395,13 @@
     <t>Bundle.type</t>
   </si>
   <si>
-    <t>document | message | transaction | transaction-response | batch | batch-response | history | searchset | collection</t>
+    <t>transaction</t>
   </si>
   <si>
     <t>Indicates the purpose of this bundle - how it is intended to be used.</t>
   </si>
   <si>
     <t>It's possible to use a bundle for other purposes (e.g. a document can be accepted as a transaction). This is primarily defined so that there can be specific rules for some of the bundle types.</t>
-  </si>
-  <si>
-    <t>transaction</t>
   </si>
   <si>
     <t>required</t>
@@ -576,7 +573,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Entry in the bundle - will have a resource or information</t>
+    <t>Entrada: recurso más su PUT condicional</t>
   </si>
   <si>
     <t>An entry in a bundle resource - will either contain a resource or information about a resource (transactions and history only).</t>
@@ -633,7 +630,7 @@
 </t>
   </si>
   <si>
-    <t>A resource in the bundle</t>
+    <t>Recurso de la entrada</t>
   </si>
   <si>
     <t>The Resource for the entry. The purpose/meaning of the resource is determined by the Bundle.type.</t>
@@ -699,7 +696,7 @@
     <t>Bundle.entry.request</t>
   </si>
   <si>
-    <t>Additional execution information (transaction/batch/history)</t>
+    <t>Operación: PUT condicional por identificador</t>
   </si>
   <si>
     <t>Additional information about how this entry should be processed as part of a transaction or batch.  For history, it shows how the entry was processed to create the version contained in the entry.</t>
@@ -721,13 +718,10 @@
     <t>Bundle.entry.request.method</t>
   </si>
   <si>
-    <t>GET | HEAD | POST | PUT | DELETE | PATCH</t>
+    <t>PUT</t>
   </si>
   <si>
     <t>In a transaction or batch, this is the HTTP action to be executed for this entry. In a history bundle, this indicates the HTTP action that occurred.</t>
-  </si>
-  <si>
-    <t>PUT</t>
   </si>
   <si>
     <t>HTTP verbs (in the HTTP command line). See [HTTP rfc](https://tools.ietf.org/html/rfc7231) for details.</t>
@@ -864,6 +858,9 @@
     <t>paciente</t>
   </si>
   <si>
+    <t>Paciente</t>
+  </si>
+  <si>
     <t>Bundle.entry:paciente.id</t>
   </si>
   <si>
@@ -890,7 +887,7 @@
 </t>
   </si>
   <si>
-    <t>Information about an individual or animal receiving health care services</t>
+    <t>Paciente (MINSALPaciente del NID)</t>
   </si>
   <si>
     <t>Demographics and other administrative information about an individual or animal receiving care or other health-related services.</t>
@@ -921,6 +918,9 @@
   </si>
   <si>
     <t>Bundle.entry:paciente.request</t>
+  </si>
+  <si>
+    <t>PUT Patient?identifier=[sistema]|[valor]</t>
   </si>
   <si>
     <t>Bundle.entry:paciente.request.id</t>
@@ -1008,7 +1008,7 @@
 </t>
   </si>
   <si>
-    <t>A grouping of people or organizations with a common purpose</t>
+    <t>Establecimiento (MINSALPrestadorOrganizacional del NID)</t>
   </si>
   <si>
     <t>A formally or informally recognized grouping of people or organizations formed for the purpose of achieving some form of collective action.  Includes companies, institutions, corporations, departments, community groups, healthcare practice groups, payer/insurer, etc.</t>
@@ -1041,6 +1041,9 @@
     <t>Bundle.entry:establecimiento.request</t>
   </si>
   <si>
+    <t>PUT Organization?identifier=[sistema DEIS]|[código]</t>
+  </si>
+  <si>
     <t>Bundle.entry:establecimiento.request.id</t>
   </si>
   <si>
@@ -1099,6 +1102,9 @@
   </si>
   <si>
     <t>profesional</t>
+  </si>
+  <si>
+    <t>Profesional (opcional)</t>
   </si>
   <si>
     <t>Bundle.entry:profesional.id</t>
@@ -1123,7 +1129,7 @@
 </t>
   </si>
   <si>
-    <t>A person with a  formal responsibility in the provisioning of healthcare or related services</t>
+    <t>Profesional (MINSALPrestadorProfesional del NID)</t>
   </si>
   <si>
     <t>A person who is directly or indirectly involved in the provisioning of healthcare.</t>
@@ -1156,6 +1162,9 @@
     <t>Bundle.entry:profesional.request</t>
   </si>
   <si>
+    <t>PUT Practitioner?identifier=[sistema]|[RUN]</t>
+  </si>
+  <si>
     <t>Bundle.entry:profesional.request.id</t>
   </si>
   <si>
@@ -1214,6 +1223,9 @@
   </si>
   <si>
     <t>encuentro</t>
+  </si>
+  <si>
+    <t>Episodio de urgencia</t>
   </si>
   <si>
     <t>Bundle.entry:encuentro.id</t>
@@ -1238,13 +1250,10 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Encounter {https://interoperabilidad.minsal.cl/fhir/ig/urgencia/StructureDefinition/encuentro-urgencia-admision}
+    <t xml:space="preserve">Encounter {https://interoperabilidad.minsal.cl/fhir/ig/urgencia-eventos/StructureDefinition/encuentro-urgencia-admision}
 </t>
   </si>
   <si>
-    <t>An interaction during which services are provided to the patient</t>
-  </si>
-  <si>
     <t>An interaction between a patient and healthcare provider(s) for the purpose of providing healthcare service(s) or assessing the health status of a patient.</t>
   </si>
   <si>
@@ -1270,6 +1279,9 @@
   </si>
   <si>
     <t>Bundle.entry:encuentro.request</t>
+  </si>
+  <si>
+    <t>PUT Encounter?identifier=[sistema DAU]|[ID DAU]</t>
   </si>
   <si>
     <t>Bundle.entry:encuentro.request.id</t>
@@ -1672,7 +1684,7 @@
     <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="89.328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="96.17578125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2553,28 +2565,28 @@
         <v>77</v>
       </c>
       <c r="S8" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X8" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="T8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X8" t="s" s="2">
+      <c r="Y8" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="Y8" t="s" s="2">
+      <c r="Z8" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="Z8" t="s" s="2">
-        <v>129</v>
       </c>
       <c r="AA8" t="s" s="2">
         <v>77</v>
@@ -2616,15 +2628,15 @@
         <v>77</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2647,16 +2659,16 @@
         <v>88</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>135</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2706,7 +2718,7 @@
         <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2727,18 +2739,18 @@
         <v>77</v>
       </c>
       <c r="AM9" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AN9" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="AN9" t="s" s="2">
-        <v>137</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2761,16 +2773,16 @@
         <v>88</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L10" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="M10" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="M10" t="s" s="2">
+      <c r="N10" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2820,7 +2832,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2829,7 +2841,7 @@
         <v>87</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>99</v>
@@ -2849,10 +2861,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2875,16 +2887,16 @@
         <v>88</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>145</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="M11" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="M11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>148</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2934,7 +2946,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2963,10 +2975,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2989,13 +3001,13 @@
         <v>77</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3046,25 +3058,25 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH12" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL12" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>77</v>
@@ -3075,14 +3087,14 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3101,16 +3113,16 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3160,7 +3172,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3172,13 +3184,13 @@
         <v>77</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>77</v>
@@ -3189,14 +3201,14 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3215,19 +3227,19 @@
         <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O14" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>77</v>
@@ -3276,7 +3288,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3288,7 +3300,7 @@
         <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>77</v>
@@ -3305,10 +3317,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3331,13 +3343,13 @@
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3388,7 +3400,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>87</v>
@@ -3417,10 +3429,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3446,10 +3458,10 @@
         <v>101</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3500,7 +3512,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>87</v>
@@ -3529,10 +3541,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3540,7 +3552,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>79</v>
@@ -3555,13 +3567,13 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3600,17 +3612,17 @@
         <v>77</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AC17" s="2"/>
       <c r="AD17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3622,7 +3634,7 @@
         <v>77</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>77</v>
@@ -3639,10 +3651,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3665,13 +3677,13 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3722,25 +3734,25 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3751,14 +3763,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3777,16 +3789,16 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3836,7 +3848,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3848,13 +3860,13 @@
         <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3865,14 +3877,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3891,19 +3903,19 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O20" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
@@ -3952,7 +3964,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3964,7 +3976,7 @@
         <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>77</v>
@@ -3981,10 +3993,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4010,10 +4022,10 @@
         <v>80</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4064,7 +4076,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4093,10 +4105,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4122,13 +4134,13 @@
         <v>101</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4178,7 +4190,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4207,10 +4219,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4233,13 +4245,13 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4290,7 +4302,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4319,10 +4331,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4345,13 +4357,13 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4402,7 +4414,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4411,7 +4423,7 @@
         <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>99</v>
@@ -4431,10 +4443,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4457,13 +4469,13 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4514,25 +4526,25 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4543,14 +4555,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4569,16 +4581,16 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4628,7 +4640,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4640,13 +4652,13 @@
         <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4657,14 +4669,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4683,19 +4695,19 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O27" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4744,7 +4756,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4756,7 +4768,7 @@
         <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>77</v>
@@ -4773,10 +4785,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4802,13 +4814,13 @@
         <v>107</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4834,14 +4846,14 @@
         <v>77</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="Z28" t="s" s="2">
-        <v>208</v>
-      </c>
       <c r="AA28" t="s" s="2">
         <v>77</v>
       </c>
@@ -4858,7 +4870,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4887,10 +4899,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4913,16 +4925,16 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4972,7 +4984,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5001,10 +5013,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5027,13 +5039,13 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5084,7 +5096,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5093,7 +5105,7 @@
         <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>99</v>
@@ -5113,10 +5125,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5139,13 +5151,13 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5196,25 +5208,25 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL31" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
@@ -5225,14 +5237,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5251,16 +5263,16 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5310,7 +5322,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5322,13 +5334,13 @@
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -5339,14 +5351,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5365,19 +5377,19 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O33" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5426,7 +5438,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5438,7 +5450,7 @@
         <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>77</v>
@@ -5455,10 +5467,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5484,10 +5496,10 @@
         <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5499,29 +5511,29 @@
         <v>77</v>
       </c>
       <c r="S34" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="Z34" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="T34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X34" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>226</v>
-      </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
       </c>
@@ -5538,7 +5550,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>87</v>
@@ -5567,10 +5579,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5596,13 +5608,13 @@
         <v>101</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5652,7 +5664,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>87</v>
@@ -5681,10 +5693,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5707,13 +5719,13 @@
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5764,7 +5776,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5793,10 +5805,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5819,13 +5831,13 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5876,7 +5888,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5905,10 +5917,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5931,13 +5943,13 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5988,7 +6000,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6017,10 +6029,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6043,13 +6055,13 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6100,7 +6112,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6129,10 +6141,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6155,13 +6167,13 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6212,7 +6224,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6221,7 +6233,7 @@
         <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>99</v>
@@ -6241,10 +6253,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6267,13 +6279,13 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6324,25 +6336,25 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL41" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6353,14 +6365,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6379,16 +6391,16 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6438,7 +6450,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6450,13 +6462,13 @@
         <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6467,14 +6479,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6493,19 +6505,19 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O43" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6554,7 +6566,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6566,7 +6578,7 @@
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
@@ -6583,10 +6595,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6609,13 +6621,13 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6666,7 +6678,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>87</v>
@@ -6695,10 +6707,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6724,10 +6736,10 @@
         <v>101</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6778,7 +6790,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6807,10 +6819,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6833,16 +6845,16 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6892,7 +6904,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6921,10 +6933,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6947,16 +6959,16 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7006,7 +7018,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7035,10 +7047,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7061,16 +7073,16 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7120,7 +7132,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7149,13 +7161,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>77</v>
@@ -7177,13 +7189,13 @@
         <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7234,7 +7246,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7246,7 +7258,7 @@
         <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
@@ -7263,10 +7275,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7289,13 +7301,13 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7346,25 +7358,25 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL50" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -7375,14 +7387,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7401,16 +7413,16 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7460,7 +7472,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7472,13 +7484,13 @@
         <v>77</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -7489,14 +7501,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7515,19 +7527,19 @@
         <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O52" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7576,7 +7588,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7588,7 +7600,7 @@
         <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>77</v>
@@ -7605,10 +7617,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7634,10 +7646,10 @@
         <v>80</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7688,7 +7700,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7717,10 +7729,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7746,13 +7758,13 @@
         <v>101</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7802,7 +7814,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7831,14 +7843,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7857,13 +7869,13 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7914,7 +7926,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7932,10 +7944,10 @@
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>77</v>
@@ -7943,10 +7955,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7969,13 +7981,13 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8026,7 +8038,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8035,7 +8047,7 @@
         <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>99</v>
@@ -8055,10 +8067,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8081,13 +8093,13 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8138,25 +8150,25 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL57" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
@@ -8167,14 +8179,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8193,16 +8205,16 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8252,7 +8264,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8264,13 +8276,13 @@
         <v>77</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
@@ -8281,14 +8293,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8307,19 +8319,19 @@
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O59" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8368,7 +8380,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8380,7 +8392,7 @@
         <v>77</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>77</v>
@@ -8397,10 +8409,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8426,13 +8438,13 @@
         <v>107</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8458,14 +8470,14 @@
         <v>77</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Y60" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="Z60" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="Z60" t="s" s="2">
-        <v>208</v>
-      </c>
       <c r="AA60" t="s" s="2">
         <v>77</v>
       </c>
@@ -8482,7 +8494,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8511,10 +8523,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8537,16 +8549,16 @@
         <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8596,7 +8608,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8625,10 +8637,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8651,13 +8663,13 @@
         <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8708,7 +8720,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8717,7 +8729,7 @@
         <v>87</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>99</v>
@@ -8740,7 +8752,7 @@
         <v>288</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8763,13 +8775,13 @@
         <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8820,25 +8832,25 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL63" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
@@ -8852,11 +8864,11 @@
         <v>289</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -8875,16 +8887,16 @@
         <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8934,7 +8946,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -8946,13 +8958,13 @@
         <v>77</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
@@ -8966,11 +8978,11 @@
         <v>290</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -8989,19 +9001,19 @@
         <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O65" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -9050,7 +9062,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9062,7 +9074,7 @@
         <v>77</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>77</v>
@@ -9082,7 +9094,7 @@
         <v>291</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9108,10 +9120,10 @@
         <v>107</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9123,29 +9135,29 @@
         <v>77</v>
       </c>
       <c r="S66" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="Z66" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="T66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>226</v>
-      </c>
       <c r="AA66" t="s" s="2">
         <v>77</v>
       </c>
@@ -9162,7 +9174,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>87</v>
@@ -9194,7 +9206,7 @@
         <v>292</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9220,13 +9232,13 @@
         <v>101</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9276,7 +9288,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>87</v>
@@ -9308,7 +9320,7 @@
         <v>293</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9331,13 +9343,13 @@
         <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9388,7 +9400,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9420,7 +9432,7 @@
         <v>294</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9443,13 +9455,13 @@
         <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9500,7 +9512,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9532,7 +9544,7 @@
         <v>295</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9555,13 +9567,13 @@
         <v>88</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9612,7 +9624,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9644,7 +9656,7 @@
         <v>296</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9667,13 +9679,13 @@
         <v>88</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9724,7 +9736,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -9756,7 +9768,7 @@
         <v>297</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9779,13 +9791,13 @@
         <v>88</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9836,7 +9848,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -9845,7 +9857,7 @@
         <v>87</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>99</v>
@@ -9868,7 +9880,7 @@
         <v>298</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9891,13 +9903,13 @@
         <v>77</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="M73" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9948,25 +9960,25 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL73" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
@@ -9980,11 +9992,11 @@
         <v>299</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10003,16 +10015,16 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10062,7 +10074,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10074,13 +10086,13 @@
         <v>77</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
@@ -10094,11 +10106,11 @@
         <v>300</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10117,19 +10129,19 @@
         <v>88</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O75" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>77</v>
@@ -10178,7 +10190,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10190,7 +10202,7 @@
         <v>77</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>77</v>
@@ -10210,7 +10222,7 @@
         <v>301</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10233,13 +10245,13 @@
         <v>88</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10290,7 +10302,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>87</v>
@@ -10322,7 +10334,7 @@
         <v>302</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10348,10 +10360,10 @@
         <v>101</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10402,7 +10414,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10434,7 +10446,7 @@
         <v>303</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10457,16 +10469,16 @@
         <v>88</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="N78" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10516,7 +10528,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10548,7 +10560,7 @@
         <v>304</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10571,16 +10583,16 @@
         <v>88</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N79" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10630,7 +10642,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -10662,7 +10674,7 @@
         <v>305</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10685,16 +10697,16 @@
         <v>88</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N80" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -10744,7 +10756,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -10776,7 +10788,7 @@
         <v>306</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C81" t="s" s="2">
         <v>307</v>
@@ -10801,13 +10813,13 @@
         <v>88</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L81" t="s" s="2">
         <v>308</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -10858,7 +10870,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -10870,7 +10882,7 @@
         <v>77</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>77</v>
@@ -10890,7 +10902,7 @@
         <v>309</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10913,13 +10925,13 @@
         <v>77</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L82" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="M82" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -10970,25 +10982,25 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL82" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>77</v>
@@ -11002,11 +11014,11 @@
         <v>310</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -11025,16 +11037,16 @@
         <v>77</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L83" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="M83" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11084,7 +11096,7 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11096,13 +11108,13 @@
         <v>77</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>77</v>
@@ -11116,11 +11128,11 @@
         <v>311</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -11139,19 +11151,19 @@
         <v>88</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O84" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>77</v>
@@ -11200,7 +11212,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -11212,7 +11224,7 @@
         <v>77</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>77</v>
@@ -11232,7 +11244,7 @@
         <v>312</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11258,10 +11270,10 @@
         <v>80</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11312,7 +11324,7 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -11344,7 +11356,7 @@
         <v>313</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11370,13 +11382,13 @@
         <v>101</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -11426,7 +11438,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -11458,7 +11470,7 @@
         <v>314</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11538,7 +11550,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -11570,7 +11582,7 @@
         <v>320</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11593,13 +11605,13 @@
         <v>88</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -11650,7 +11662,7 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -11659,7 +11671,7 @@
         <v>87</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>99</v>
@@ -11682,7 +11694,7 @@
         <v>321</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11705,13 +11717,13 @@
         <v>77</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L89" t="s" s="2">
+      <c r="M89" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -11762,25 +11774,25 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL89" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG89" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>77</v>
@@ -11794,11 +11806,11 @@
         <v>322</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -11817,16 +11829,16 @@
         <v>77</v>
       </c>
       <c r="K90" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L90" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L90" t="s" s="2">
+      <c r="M90" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -11876,7 +11888,7 @@
         <v>77</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -11888,13 +11900,13 @@
         <v>77</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>77</v>
@@ -11908,11 +11920,11 @@
         <v>323</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -11931,19 +11943,19 @@
         <v>88</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O91" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>77</v>
@@ -11992,7 +12004,7 @@
         <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -12004,7 +12016,7 @@
         <v>77</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>77</v>
@@ -12024,7 +12036,7 @@
         <v>324</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12050,13 +12062,13 @@
         <v>107</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12082,14 +12094,14 @@
         <v>77</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Y92" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="Z92" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="Z92" t="s" s="2">
-        <v>208</v>
-      </c>
       <c r="AA92" t="s" s="2">
         <v>77</v>
       </c>
@@ -12106,7 +12118,7 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -12138,7 +12150,7 @@
         <v>325</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12161,16 +12173,16 @@
         <v>88</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L93" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="M93" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12220,7 +12232,7 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -12252,7 +12264,7 @@
         <v>326</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12275,13 +12287,13 @@
         <v>88</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -12332,7 +12344,7 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -12341,7 +12353,7 @@
         <v>87</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>99</v>
@@ -12361,10 +12373,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12387,13 +12399,13 @@
         <v>77</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="M95" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -12444,25 +12456,25 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL95" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH95" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI95" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ95" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK95" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>77</v>
@@ -12473,14 +12485,14 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -12499,16 +12511,16 @@
         <v>77</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L96" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L96" t="s" s="2">
+      <c r="M96" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -12558,7 +12570,7 @@
         <v>77</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -12570,13 +12582,13 @@
         <v>77</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>77</v>
@@ -12587,14 +12599,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -12613,19 +12625,19 @@
         <v>88</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="N97" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O97" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>77</v>
@@ -12674,7 +12686,7 @@
         <v>77</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -12686,7 +12698,7 @@
         <v>77</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>77</v>
@@ -12703,10 +12715,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12732,10 +12744,10 @@
         <v>107</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -12747,29 +12759,29 @@
         <v>77</v>
       </c>
       <c r="S98" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="Z98" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="T98" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U98" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V98" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W98" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X98" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="Z98" t="s" s="2">
-        <v>226</v>
-      </c>
       <c r="AA98" t="s" s="2">
         <v>77</v>
       </c>
@@ -12786,7 +12798,7 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>87</v>
@@ -12815,10 +12827,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12844,13 +12856,13 @@
         <v>101</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="N99" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -12900,7 +12912,7 @@
         <v>77</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>87</v>
@@ -12929,10 +12941,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12955,13 +12967,13 @@
         <v>88</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13012,7 +13024,7 @@
         <v>77</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -13041,10 +13053,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13067,13 +13079,13 @@
         <v>88</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -13124,7 +13136,7 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -13153,10 +13165,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13179,13 +13191,13 @@
         <v>88</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -13236,7 +13248,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -13265,10 +13277,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13291,13 +13303,13 @@
         <v>88</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -13348,7 +13360,7 @@
         <v>77</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -13377,10 +13389,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13403,13 +13415,13 @@
         <v>88</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -13460,7 +13472,7 @@
         <v>77</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -13469,7 +13481,7 @@
         <v>87</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>99</v>
@@ -13489,10 +13501,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13515,13 +13527,13 @@
         <v>77</v>
       </c>
       <c r="K105" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L105" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L105" t="s" s="2">
+      <c r="M105" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -13572,25 +13584,25 @@
         <v>77</v>
       </c>
       <c r="AF105" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL105" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH105" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL105" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>77</v>
@@ -13601,14 +13613,14 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -13627,16 +13639,16 @@
         <v>77</v>
       </c>
       <c r="K106" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L106" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L106" t="s" s="2">
+      <c r="M106" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M106" t="s" s="2">
+      <c r="N106" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -13686,7 +13698,7 @@
         <v>77</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -13698,13 +13710,13 @@
         <v>77</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>77</v>
@@ -13715,14 +13727,14 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -13741,19 +13753,19 @@
         <v>88</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="N107" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O107" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>77</v>
@@ -13802,7 +13814,7 @@
         <v>77</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -13814,7 +13826,7 @@
         <v>77</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>77</v>
@@ -13831,10 +13843,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13857,13 +13869,13 @@
         <v>88</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -13914,7 +13926,7 @@
         <v>77</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>87</v>
@@ -13943,10 +13955,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13972,10 +13984,10 @@
         <v>101</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -14026,7 +14038,7 @@
         <v>77</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -14055,10 +14067,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14081,16 +14093,16 @@
         <v>88</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="N110" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -14140,7 +14152,7 @@
         <v>77</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -14169,10 +14181,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14195,16 +14207,16 @@
         <v>88</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N111" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -14254,7 +14266,7 @@
         <v>77</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -14283,10 +14295,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14309,16 +14321,16 @@
         <v>88</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N112" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -14368,7 +14380,7 @@
         <v>77</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -14397,13 +14409,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D113" t="s" s="2">
         <v>77</v>
@@ -14425,13 +14437,13 @@
         <v>88</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L113" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -14482,7 +14494,7 @@
         <v>77</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -14494,7 +14506,7 @@
         <v>77</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>77</v>
@@ -14511,10 +14523,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14537,13 +14549,13 @@
         <v>77</v>
       </c>
       <c r="K114" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L114" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L114" t="s" s="2">
+      <c r="M114" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -14594,25 +14606,25 @@
         <v>77</v>
       </c>
       <c r="AF114" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL114" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH114" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL114" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>77</v>
@@ -14623,14 +14635,14 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
@@ -14649,16 +14661,16 @@
         <v>77</v>
       </c>
       <c r="K115" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L115" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L115" t="s" s="2">
+      <c r="M115" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M115" t="s" s="2">
+      <c r="N115" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -14708,7 +14720,7 @@
         <v>77</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -14720,13 +14732,13 @@
         <v>77</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>77</v>
@@ -14737,14 +14749,14 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -14763,19 +14775,19 @@
         <v>88</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M116" t="s" s="2">
+      <c r="N116" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O116" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>77</v>
@@ -14824,7 +14836,7 @@
         <v>77</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -14836,7 +14848,7 @@
         <v>77</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>77</v>
@@ -14853,10 +14865,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14882,10 +14894,10 @@
         <v>80</v>
       </c>
       <c r="L117" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M117" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -14936,7 +14948,7 @@
         <v>77</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
@@ -14965,10 +14977,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14994,13 +15006,13 @@
         <v>101</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M118" t="s" s="2">
+      <c r="N118" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -15050,7 +15062,7 @@
         <v>77</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
@@ -15079,10 +15091,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15105,13 +15117,13 @@
         <v>77</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -15162,7 +15174,7 @@
         <v>77</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>78</v>
@@ -15177,10 +15189,10 @@
         <v>77</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>77</v>
@@ -15191,10 +15203,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15217,13 +15229,13 @@
         <v>88</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -15274,7 +15286,7 @@
         <v>77</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -15283,7 +15295,7 @@
         <v>87</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AJ120" t="s" s="2">
         <v>99</v>
@@ -15303,10 +15315,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15329,13 +15341,13 @@
         <v>77</v>
       </c>
       <c r="K121" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L121" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L121" t="s" s="2">
+      <c r="M121" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -15386,25 +15398,25 @@
         <v>77</v>
       </c>
       <c r="AF121" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL121" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH121" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL121" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>77</v>
@@ -15415,14 +15427,14 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -15441,16 +15453,16 @@
         <v>77</v>
       </c>
       <c r="K122" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L122" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L122" t="s" s="2">
+      <c r="M122" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M122" t="s" s="2">
+      <c r="N122" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -15500,7 +15512,7 @@
         <v>77</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -15512,13 +15524,13 @@
         <v>77</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>77</v>
@@ -15529,14 +15541,14 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
@@ -15555,19 +15567,19 @@
         <v>88</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M123" t="s" s="2">
+      <c r="N123" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O123" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>77</v>
@@ -15616,7 +15628,7 @@
         <v>77</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -15628,7 +15640,7 @@
         <v>77</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>77</v>
@@ -15645,10 +15657,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15674,13 +15686,13 @@
         <v>107</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M124" t="s" s="2">
+      <c r="N124" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -15706,14 +15718,14 @@
         <v>77</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Y124" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="Z124" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="Z124" t="s" s="2">
-        <v>208</v>
-      </c>
       <c r="AA124" t="s" s="2">
         <v>77</v>
       </c>
@@ -15730,7 +15742,7 @@
         <v>77</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -15759,10 +15771,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15785,16 +15797,16 @@
         <v>88</v>
       </c>
       <c r="K125" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L125" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L125" t="s" s="2">
+      <c r="M125" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="M125" t="s" s="2">
+      <c r="N125" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -15844,7 +15856,7 @@
         <v>77</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -15873,10 +15885,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15899,13 +15911,13 @@
         <v>88</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -15956,7 +15968,7 @@
         <v>77</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -15965,7 +15977,7 @@
         <v>87</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>99</v>
@@ -15985,10 +15997,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16011,13 +16023,13 @@
         <v>77</v>
       </c>
       <c r="K127" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L127" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L127" t="s" s="2">
+      <c r="M127" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -16068,25 +16080,25 @@
         <v>77</v>
       </c>
       <c r="AF127" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL127" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH127" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL127" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>77</v>
@@ -16097,14 +16109,14 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -16123,16 +16135,16 @@
         <v>77</v>
       </c>
       <c r="K128" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L128" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L128" t="s" s="2">
+      <c r="M128" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M128" t="s" s="2">
+      <c r="N128" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -16182,7 +16194,7 @@
         <v>77</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>78</v>
@@ -16194,13 +16206,13 @@
         <v>77</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK128" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>77</v>
@@ -16211,14 +16223,14 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
@@ -16237,19 +16249,19 @@
         <v>88</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L129" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M129" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M129" t="s" s="2">
+      <c r="N129" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O129" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O129" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>77</v>
@@ -16298,7 +16310,7 @@
         <v>77</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>78</v>
@@ -16310,7 +16322,7 @@
         <v>77</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>77</v>
@@ -16327,10 +16339,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -16356,10 +16368,10 @@
         <v>107</v>
       </c>
       <c r="L130" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M130" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -16371,29 +16383,29 @@
         <v>77</v>
       </c>
       <c r="S130" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="T130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X130" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="Z130" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="T130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X130" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="Y130" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="Z130" t="s" s="2">
-        <v>226</v>
-      </c>
       <c r="AA130" t="s" s="2">
         <v>77</v>
       </c>
@@ -16410,7 +16422,7 @@
         <v>77</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>87</v>
@@ -16439,10 +16451,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -16468,13 +16480,13 @@
         <v>101</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="N131" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -16524,7 +16536,7 @@
         <v>77</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>87</v>
@@ -16553,10 +16565,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -16579,13 +16591,13 @@
         <v>88</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -16636,7 +16648,7 @@
         <v>77</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>78</v>
@@ -16665,10 +16677,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -16691,13 +16703,13 @@
         <v>88</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -16748,7 +16760,7 @@
         <v>77</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>78</v>
@@ -16777,10 +16789,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -16803,13 +16815,13 @@
         <v>88</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -16860,7 +16872,7 @@
         <v>77</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>78</v>
@@ -16889,10 +16901,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -16915,13 +16927,13 @@
         <v>88</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -16972,7 +16984,7 @@
         <v>77</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>78</v>
@@ -17001,10 +17013,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17027,13 +17039,13 @@
         <v>88</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -17084,7 +17096,7 @@
         <v>77</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>78</v>
@@ -17093,7 +17105,7 @@
         <v>87</v>
       </c>
       <c r="AI136" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AJ136" t="s" s="2">
         <v>99</v>
@@ -17113,10 +17125,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17139,13 +17151,13 @@
         <v>77</v>
       </c>
       <c r="K137" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L137" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L137" t="s" s="2">
+      <c r="M137" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M137" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
@@ -17196,25 +17208,25 @@
         <v>77</v>
       </c>
       <c r="AF137" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH137" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI137" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ137" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK137" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL137" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH137" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI137" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ137" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK137" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL137" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>77</v>
@@ -17225,14 +17237,14 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -17251,16 +17263,16 @@
         <v>77</v>
       </c>
       <c r="K138" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L138" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L138" t="s" s="2">
+      <c r="M138" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M138" t="s" s="2">
+      <c r="N138" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -17310,7 +17322,7 @@
         <v>77</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>78</v>
@@ -17322,13 +17334,13 @@
         <v>77</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM138" t="s" s="2">
         <v>77</v>
@@ -17339,14 +17351,14 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
@@ -17365,19 +17377,19 @@
         <v>88</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L139" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M139" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M139" t="s" s="2">
+      <c r="N139" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O139" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O139" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>77</v>
@@ -17426,7 +17438,7 @@
         <v>77</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>78</v>
@@ -17438,7 +17450,7 @@
         <v>77</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK139" t="s" s="2">
         <v>77</v>
@@ -17455,10 +17467,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -17481,13 +17493,13 @@
         <v>88</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -17538,7 +17550,7 @@
         <v>77</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>87</v>
@@ -17567,10 +17579,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -17596,10 +17608,10 @@
         <v>101</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -17650,7 +17662,7 @@
         <v>77</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>78</v>
@@ -17679,10 +17691,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -17705,16 +17717,16 @@
         <v>88</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L142" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M142" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="N142" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -17764,7 +17776,7 @@
         <v>77</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>78</v>
@@ -17793,10 +17805,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -17819,16 +17831,16 @@
         <v>88</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L143" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M143" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N143" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="M143" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -17878,7 +17890,7 @@
         <v>77</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>78</v>
@@ -17907,10 +17919,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -17933,16 +17945,16 @@
         <v>88</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L144" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M144" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N144" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="M144" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N144" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -17992,7 +18004,7 @@
         <v>77</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>78</v>
@@ -18021,13 +18033,13 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="D145" t="s" s="2">
         <v>77</v>
@@ -18049,13 +18061,13 @@
         <v>88</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L145" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M145" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="M145" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -18106,7 +18118,7 @@
         <v>77</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>78</v>
@@ -18118,7 +18130,7 @@
         <v>77</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AK145" t="s" s="2">
         <v>77</v>
@@ -18135,10 +18147,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -18161,13 +18173,13 @@
         <v>77</v>
       </c>
       <c r="K146" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L146" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L146" t="s" s="2">
+      <c r="M146" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M146" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -18218,25 +18230,25 @@
         <v>77</v>
       </c>
       <c r="AF146" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH146" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI146" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ146" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK146" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL146" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH146" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI146" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ146" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK146" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL146" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM146" t="s" s="2">
         <v>77</v>
@@ -18247,14 +18259,14 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
@@ -18273,16 +18285,16 @@
         <v>77</v>
       </c>
       <c r="K147" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L147" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L147" t="s" s="2">
+      <c r="M147" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M147" t="s" s="2">
+      <c r="N147" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -18332,7 +18344,7 @@
         <v>77</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>78</v>
@@ -18344,13 +18356,13 @@
         <v>77</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK147" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM147" t="s" s="2">
         <v>77</v>
@@ -18361,14 +18373,14 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
@@ -18387,19 +18399,19 @@
         <v>88</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L148" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M148" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M148" t="s" s="2">
+      <c r="N148" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O148" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O148" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>77</v>
@@ -18448,7 +18460,7 @@
         <v>77</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>78</v>
@@ -18460,7 +18472,7 @@
         <v>77</v>
       </c>
       <c r="AJ148" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK148" t="s" s="2">
         <v>77</v>
@@ -18477,10 +18489,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -18506,10 +18518,10 @@
         <v>80</v>
       </c>
       <c r="L149" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M149" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="M149" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -18560,7 +18572,7 @@
         <v>77</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>78</v>
@@ -18589,10 +18601,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -18618,13 +18630,13 @@
         <v>101</v>
       </c>
       <c r="L150" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M150" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M150" t="s" s="2">
+      <c r="N150" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="N150" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -18674,7 +18686,7 @@
         <v>77</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>78</v>
@@ -18703,14 +18715,14 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
@@ -18729,13 +18741,13 @@
         <v>77</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -18786,7 +18798,7 @@
         <v>77</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>78</v>
@@ -18804,7 +18816,7 @@
         <v>77</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>77</v>
@@ -18815,10 +18827,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -18841,13 +18853,13 @@
         <v>88</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L152" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M152" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="M152" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -18898,7 +18910,7 @@
         <v>77</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>78</v>
@@ -18907,7 +18919,7 @@
         <v>87</v>
       </c>
       <c r="AI152" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AJ152" t="s" s="2">
         <v>99</v>
@@ -18927,10 +18939,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -18953,13 +18965,13 @@
         <v>77</v>
       </c>
       <c r="K153" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L153" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L153" t="s" s="2">
+      <c r="M153" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M153" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -19010,25 +19022,25 @@
         <v>77</v>
       </c>
       <c r="AF153" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH153" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI153" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ153" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK153" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL153" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH153" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI153" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ153" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK153" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL153" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM153" t="s" s="2">
         <v>77</v>
@@ -19039,14 +19051,14 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
@@ -19065,16 +19077,16 @@
         <v>77</v>
       </c>
       <c r="K154" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L154" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L154" t="s" s="2">
+      <c r="M154" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M154" t="s" s="2">
+      <c r="N154" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -19124,7 +19136,7 @@
         <v>77</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>78</v>
@@ -19136,13 +19148,13 @@
         <v>77</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK154" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM154" t="s" s="2">
         <v>77</v>
@@ -19153,14 +19165,14 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
@@ -19179,19 +19191,19 @@
         <v>88</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L155" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M155" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M155" t="s" s="2">
+      <c r="N155" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O155" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N155" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O155" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>77</v>
@@ -19240,7 +19252,7 @@
         <v>77</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>78</v>
@@ -19252,7 +19264,7 @@
         <v>77</v>
       </c>
       <c r="AJ155" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK155" t="s" s="2">
         <v>77</v>
@@ -19269,10 +19281,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -19298,13 +19310,13 @@
         <v>107</v>
       </c>
       <c r="L156" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M156" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M156" t="s" s="2">
+      <c r="N156" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -19330,14 +19342,14 @@
         <v>77</v>
       </c>
       <c r="X156" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Y156" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="Z156" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="Z156" t="s" s="2">
-        <v>208</v>
-      </c>
       <c r="AA156" t="s" s="2">
         <v>77</v>
       </c>
@@ -19354,7 +19366,7 @@
         <v>77</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>78</v>
@@ -19383,10 +19395,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -19409,16 +19421,16 @@
         <v>88</v>
       </c>
       <c r="K157" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L157" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L157" t="s" s="2">
+      <c r="M157" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="M157" t="s" s="2">
+      <c r="N157" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -19468,7 +19480,7 @@
         <v>77</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>78</v>
@@ -19497,10 +19509,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -19523,13 +19535,13 @@
         <v>88</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L158" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M158" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="M158" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -19580,7 +19592,7 @@
         <v>77</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>78</v>
@@ -19589,7 +19601,7 @@
         <v>87</v>
       </c>
       <c r="AI158" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AJ158" t="s" s="2">
         <v>99</v>
@@ -19609,10 +19621,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -19635,13 +19647,13 @@
         <v>77</v>
       </c>
       <c r="K159" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L159" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L159" t="s" s="2">
+      <c r="M159" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M159" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
@@ -19692,25 +19704,25 @@
         <v>77</v>
       </c>
       <c r="AF159" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH159" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI159" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ159" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK159" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL159" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH159" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI159" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ159" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK159" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL159" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM159" t="s" s="2">
         <v>77</v>
@@ -19721,14 +19733,14 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
@@ -19747,16 +19759,16 @@
         <v>77</v>
       </c>
       <c r="K160" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L160" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L160" t="s" s="2">
+      <c r="M160" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M160" t="s" s="2">
+      <c r="N160" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N160" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
@@ -19806,7 +19818,7 @@
         <v>77</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>78</v>
@@ -19818,13 +19830,13 @@
         <v>77</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK160" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM160" t="s" s="2">
         <v>77</v>
@@ -19835,14 +19847,14 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
@@ -19861,19 +19873,19 @@
         <v>88</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L161" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M161" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M161" t="s" s="2">
+      <c r="N161" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O161" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N161" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O161" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>77</v>
@@ -19922,7 +19934,7 @@
         <v>77</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>78</v>
@@ -19934,7 +19946,7 @@
         <v>77</v>
       </c>
       <c r="AJ161" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK161" t="s" s="2">
         <v>77</v>
@@ -19951,10 +19963,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -19980,10 +19992,10 @@
         <v>107</v>
       </c>
       <c r="L162" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M162" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="M162" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -19995,29 +20007,29 @@
         <v>77</v>
       </c>
       <c r="S162" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="T162" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U162" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V162" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W162" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X162" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="Y162" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="Z162" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="T162" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U162" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V162" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W162" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X162" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="Y162" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="Z162" t="s" s="2">
-        <v>226</v>
-      </c>
       <c r="AA162" t="s" s="2">
         <v>77</v>
       </c>
@@ -20034,7 +20046,7 @@
         <v>77</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>87</v>
@@ -20063,10 +20075,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -20092,13 +20104,13 @@
         <v>101</v>
       </c>
       <c r="L163" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M163" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="N163" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="M163" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N163" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
@@ -20148,7 +20160,7 @@
         <v>77</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>87</v>
@@ -20177,10 +20189,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -20203,13 +20215,13 @@
         <v>88</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
@@ -20260,7 +20272,7 @@
         <v>77</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>78</v>
@@ -20289,10 +20301,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -20315,13 +20327,13 @@
         <v>88</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -20372,7 +20384,7 @@
         <v>77</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>78</v>
@@ -20401,10 +20413,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -20427,13 +20439,13 @@
         <v>88</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -20484,7 +20496,7 @@
         <v>77</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>78</v>
@@ -20513,10 +20525,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -20539,13 +20551,13 @@
         <v>88</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -20596,7 +20608,7 @@
         <v>77</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>78</v>
@@ -20625,10 +20637,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -20651,13 +20663,13 @@
         <v>88</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -20708,7 +20720,7 @@
         <v>77</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>78</v>
@@ -20717,7 +20729,7 @@
         <v>87</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AJ168" t="s" s="2">
         <v>99</v>
@@ -20737,10 +20749,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -20763,13 +20775,13 @@
         <v>77</v>
       </c>
       <c r="K169" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L169" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L169" t="s" s="2">
+      <c r="M169" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M169" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -20820,25 +20832,25 @@
         <v>77</v>
       </c>
       <c r="AF169" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG169" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH169" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI169" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ169" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK169" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL169" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG169" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH169" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI169" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ169" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK169" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL169" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM169" t="s" s="2">
         <v>77</v>
@@ -20849,14 +20861,14 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E170" s="2"/>
       <c r="F170" t="s" s="2">
@@ -20875,16 +20887,16 @@
         <v>77</v>
       </c>
       <c r="K170" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L170" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L170" t="s" s="2">
+      <c r="M170" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M170" t="s" s="2">
+      <c r="N170" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N170" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
@@ -20934,7 +20946,7 @@
         <v>77</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>78</v>
@@ -20946,13 +20958,13 @@
         <v>77</v>
       </c>
       <c r="AJ170" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK170" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL170" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM170" t="s" s="2">
         <v>77</v>
@@ -20963,14 +20975,14 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E171" s="2"/>
       <c r="F171" t="s" s="2">
@@ -20989,19 +21001,19 @@
         <v>88</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L171" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M171" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M171" t="s" s="2">
+      <c r="N171" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O171" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N171" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O171" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>77</v>
@@ -21050,7 +21062,7 @@
         <v>77</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>78</v>
@@ -21062,7 +21074,7 @@
         <v>77</v>
       </c>
       <c r="AJ171" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK171" t="s" s="2">
         <v>77</v>
@@ -21079,10 +21091,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -21105,13 +21117,13 @@
         <v>88</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -21162,7 +21174,7 @@
         <v>77</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>87</v>
@@ -21191,10 +21203,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -21220,10 +21232,10 @@
         <v>101</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -21274,7 +21286,7 @@
         <v>77</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>78</v>
@@ -21303,10 +21315,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -21329,16 +21341,16 @@
         <v>88</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L174" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M174" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="N174" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="M174" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N174" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
@@ -21388,7 +21400,7 @@
         <v>77</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>78</v>
@@ -21417,10 +21429,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -21443,16 +21455,16 @@
         <v>88</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L175" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M175" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N175" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="M175" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N175" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -21502,7 +21514,7 @@
         <v>77</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>78</v>
@@ -21531,10 +21543,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -21557,16 +21569,16 @@
         <v>88</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L176" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M176" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N176" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="M176" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N176" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
@@ -21616,7 +21628,7 @@
         <v>77</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>78</v>
@@ -21645,10 +21657,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -21671,19 +21683,19 @@
         <v>88</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="O177" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>77</v>
@@ -21732,7 +21744,7 @@
         <v>77</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>78</v>

--- a/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-bundle-admision-urgencia.xlsx
+++ b/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-bundle-admision-urgencia.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6348" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6348" uniqueCount="433">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:47:41-03:00</t>
+    <t>2026-10-08T00:02:21-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Evento admisión: el paciente es admitido en urgencia. Abre el episodio (Encounter en in-progress) y avisa a la red que el paciente se encuentra en atención.</t>
+    <t>Evento admisión: el paciente es admitido en urgencia. Abre el episodio (Encounter en arrived) y avisa a la red que el paciente está en la unidad de urgencia.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -269,7 +269,7 @@
   </si>
   <si>
     <t>bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}
-bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}urg-tx-put-condicional:Todas las entradas deben usar PUT condicional por identificador: request.method = PUT y request.url = [Tipo]?identifier=[system]|[value]. {entry.all(request.method = 'PUT' and request.url.contains('?identifier=') and request.url.contains('|'))}</t>
+bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}urg-tx-maestros:Patient, Organization y Practitioner se envían solo con creación condicional: request.method = POST, request.url = [Tipo] y request.ifNoneExist = identifier=[system]|[value]. Nunca se actualizan. {entry.where(resource is Patient or resource is Organization or resource is Practitioner).all(request.method = 'POST' and request.ifNoneExist.startsWith('identifier=') and request.ifNoneExist.contains('|'))}urg-tx-put-condicional:Los recursos del episodio (Encounter, Condition, MedicationRequest, DocumentReference) se envían con PUT condicional: request.method = PUT y request.url = [Tipo]?identifier=[system]|[value]. {entry.where((resource is Patient or resource is Organization or resource is Practitioner).not()).all(request.method = 'PUT' and request.url.contains('?identifier=') and request.url.contains('|'))}urg-tx-sin-id:Los recursos enviados con PUT condicional no llevan Resource.id: el id lo determina el servidor al encontrar (o crear) el recurso por su identificador. {entry.where(request.method = 'PUT').all(resource.id.empty())}urg-tx-identificador:El identificador de la operación condicional (request.url o request.ifNoneExist) debe ser el mismo que trae el recurso (identifier o masterIdentifier). {entry.where(request.method = 'PUT').select(request.url.substring(request.url.indexOf('|') + 1) in (resource.identifier.value | resource.masterIdentifier.value)).allTrue() and entry.where(request.method = 'POST').select(request.ifNoneExist.substring(request.ifNoneExist.indexOf('|') + 1) in resource.identifier.value).allTrue()}urg-tx-mismo-paciente:Todos los recursos del Bundle se refieren al mismo paciente: su subject apunta a la entrada del paciente. {(entry.resource.ofType(Encounter) | entry.resource.ofType(Condition) | entry.resource.ofType(MedicationRequest) | entry.resource.ofType(DocumentReference)).all(subject.reference = %resource.entry.where(resource is Patient).fullUrl.first())}urg-tx-restringido:Si el episodio está marcado como restringido (meta.security = R), también deben estarlo sus diagnósticos, indicaciones y documento. {entry.resource.ofType(Encounter).meta.security.where(code = 'R').exists() implies (entry.resource.ofType(Condition) | entry.resource.ofType(MedicationRequest) | entry.resource.ofType(DocumentReference)).all(meta.security.where(system = 'http://terminology.hl7.org/CodeSystem/v3-Confidentiality' and code = 'R').exists())}</t>
   </si>
   <si>
     <t>N/A</t>
@@ -573,7 +573,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Entrada: recurso más su PUT condicional</t>
+    <t>Entrada: recurso más su operación condicional</t>
   </si>
   <si>
     <t>An entry in a bundle resource - will either contain a resource or information about a resource (transactions and history only).</t>
@@ -696,7 +696,7 @@
     <t>Bundle.entry.request</t>
   </si>
   <si>
-    <t>Operación: PUT condicional por identificador</t>
+    <t>POST con ifNoneExist (maestros) o PUT condicional (episodio)</t>
   </si>
   <si>
     <t>Additional information about how this entry should be processed as part of a transaction or batch.  For history, it shows how the entry was processed to create the version contained in the entry.</t>
@@ -718,7 +718,7 @@
     <t>Bundle.entry.request.method</t>
   </si>
   <si>
-    <t>PUT</t>
+    <t>POST (maestros) | PUT (episodio)</t>
   </si>
   <si>
     <t>In a transaction or batch, this is the HTTP action to be executed for this entry. In a history bundle, this indicates the HTTP action that occurred.</t>
@@ -733,7 +733,7 @@
     <t>Bundle.entry.request.url</t>
   </si>
   <si>
-    <t>[Tipo]?identifier=[system]|[value]</t>
+    <t>[Tipo] (maestros) o [Tipo]?identifier=[sistema]|[valor] (episodio)</t>
   </si>
   <si>
     <t>The URL for this entry, relative to the root (the address to which the request is posted).</t>
@@ -769,7 +769,7 @@
     <t>Bundle.entry.request.ifNoneExist</t>
   </si>
   <si>
-    <t>For conditional creates</t>
+    <t>identifier=[sistema]|[valor] (solo maestros)</t>
   </si>
   <si>
     <t>Instruct the server not to perform the create if a specified resource already exists. For further information, see the API documentation for ["Conditional Create"](http://hl7.org/fhir/R4/http.html#ccreate). This is just the query portion of the URL - what follows the "?" (not including the "?").</t>
@@ -920,7 +920,7 @@
     <t>Bundle.entry:paciente.request</t>
   </si>
   <si>
-    <t>PUT Patient?identifier=[sistema]|[valor]</t>
+    <t>POST Patient, ifNoneExist identifier=[sistema]|[valor]</t>
   </si>
   <si>
     <t>Bundle.entry:paciente.request.id</t>
@@ -933,6 +933,9 @@
   </si>
   <si>
     <t>Bundle.entry:paciente.request.method</t>
+  </si>
+  <si>
+    <t>POST</t>
   </si>
   <si>
     <t>Bundle.entry:paciente.request.url</t>
@@ -1041,7 +1044,7 @@
     <t>Bundle.entry:establecimiento.request</t>
   </si>
   <si>
-    <t>PUT Organization?identifier=[sistema DEIS]|[código]</t>
+    <t>POST Organization, ifNoneExist identifier=[sistema DEIS]|[código]</t>
   </si>
   <si>
     <t>Bundle.entry:establecimiento.request.id</t>
@@ -1162,7 +1165,7 @@
     <t>Bundle.entry:profesional.request</t>
   </si>
   <si>
-    <t>PUT Practitioner?identifier=[sistema]|[RUN]</t>
+    <t>POST Practitioner, ifNoneExist identifier=[sistema]|[RUN]</t>
   </si>
   <si>
     <t>Bundle.entry:profesional.request.id</t>
@@ -1254,7 +1257,7 @@
 </t>
   </si>
   <si>
-    <t>An interaction between a patient and healthcare provider(s) for the purpose of providing healthcare service(s) or assessing the health status of a patient.</t>
+    <t>Episodio de atención en una unidad de urgencia. Se envía SIEMPRE COMPLETO en cada evento: el PUT condicional reemplaza el recurso entero, por lo que el alta y el abandono deben repetir todos los datos informados en la admisión (previsión, procedencia, medio de llegada, motivo de consulta, etc.). Un dato omitido en el alta se borra del repositorio.</t>
   </si>
   <si>
     <t>Encounter[@moodCode='EVN']</t>
@@ -1294,6 +1297,9 @@
   </si>
   <si>
     <t>Bundle.entry:encuentro.request.method</t>
+  </si>
+  <si>
+    <t>PUT</t>
   </si>
   <si>
     <t>Bundle.entry:encuentro.request.url</t>
@@ -5511,7 +5517,7 @@
         <v>77</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>221</v>
+        <v>77</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>77</v>
@@ -9135,7 +9141,7 @@
         <v>77</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>221</v>
+        <v>292</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>77</v>
@@ -9203,7 +9209,7 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>225</v>
@@ -9317,7 +9323,7 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>229</v>
@@ -9429,7 +9435,7 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>232</v>
@@ -9541,7 +9547,7 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>234</v>
@@ -9653,7 +9659,7 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>237</v>
@@ -9664,7 +9670,7 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>87</v>
@@ -9765,7 +9771,7 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>240</v>
@@ -9877,7 +9883,7 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>244</v>
@@ -9989,7 +9995,7 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>245</v>
@@ -10103,7 +10109,7 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>246</v>
@@ -10219,7 +10225,7 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>247</v>
@@ -10331,7 +10337,7 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>250</v>
@@ -10443,7 +10449,7 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>253</v>
@@ -10557,7 +10563,7 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>257</v>
@@ -10671,7 +10677,7 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>261</v>
@@ -10785,13 +10791,13 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>174</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>77</v>
@@ -10816,7 +10822,7 @@
         <v>144</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M81" t="s" s="2">
         <v>177</v>
@@ -10899,7 +10905,7 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>181</v>
@@ -11011,7 +11017,7 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>182</v>
@@ -11125,7 +11131,7 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>183</v>
@@ -11241,7 +11247,7 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>184</v>
@@ -11353,7 +11359,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>187</v>
@@ -11467,7 +11473,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>191</v>
@@ -11493,13 +11499,13 @@
         <v>77</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -11565,10 +11571,10 @@
         <v>77</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>77</v>
@@ -11579,7 +11585,7 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>195</v>
@@ -11691,7 +11697,7 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>199</v>
@@ -11803,7 +11809,7 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>200</v>
@@ -11917,7 +11923,7 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>201</v>
@@ -12033,7 +12039,7 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>202</v>
@@ -12147,7 +12153,7 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>208</v>
@@ -12261,7 +12267,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>213</v>
@@ -12290,7 +12296,7 @@
         <v>144</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M94" t="s" s="2">
         <v>215</v>
@@ -12373,7 +12379,7 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>217</v>
@@ -12485,7 +12491,7 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>218</v>
@@ -12599,7 +12605,7 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>219</v>
@@ -12715,7 +12721,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>220</v>
@@ -12759,7 +12765,7 @@
         <v>77</v>
       </c>
       <c r="S98" t="s" s="2">
-        <v>221</v>
+        <v>292</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>77</v>
@@ -12827,7 +12833,7 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>225</v>
@@ -12941,7 +12947,7 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>229</v>
@@ -13053,7 +13059,7 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>232</v>
@@ -13165,7 +13171,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>234</v>
@@ -13277,7 +13283,7 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>237</v>
@@ -13288,7 +13294,7 @@
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G103" t="s" s="2">
         <v>87</v>
@@ -13389,7 +13395,7 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>240</v>
@@ -13501,7 +13507,7 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>244</v>
@@ -13613,7 +13619,7 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>245</v>
@@ -13727,7 +13733,7 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>246</v>
@@ -13843,7 +13849,7 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>247</v>
@@ -13955,7 +13961,7 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>250</v>
@@ -14067,7 +14073,7 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>253</v>
@@ -14181,7 +14187,7 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>257</v>
@@ -14295,7 +14301,7 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>261</v>
@@ -14409,13 +14415,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>174</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D113" t="s" s="2">
         <v>77</v>
@@ -14440,7 +14446,7 @@
         <v>144</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M113" t="s" s="2">
         <v>177</v>
@@ -14523,7 +14529,7 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>181</v>
@@ -14635,7 +14641,7 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>182</v>
@@ -14749,7 +14755,7 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>183</v>
@@ -14865,7 +14871,7 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>184</v>
@@ -14977,7 +14983,7 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>187</v>
@@ -15091,7 +15097,7 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>191</v>
@@ -15117,13 +15123,13 @@
         <v>77</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -15189,10 +15195,10 @@
         <v>77</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>77</v>
@@ -15203,7 +15209,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>195</v>
@@ -15315,7 +15321,7 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>199</v>
@@ -15427,7 +15433,7 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>200</v>
@@ -15541,7 +15547,7 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>201</v>
@@ -15657,7 +15663,7 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>202</v>
@@ -15771,7 +15777,7 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>208</v>
@@ -15885,7 +15891,7 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>213</v>
@@ -15914,7 +15920,7 @@
         <v>144</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M126" t="s" s="2">
         <v>215</v>
@@ -15997,7 +16003,7 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>217</v>
@@ -16109,7 +16115,7 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>218</v>
@@ -16223,7 +16229,7 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>219</v>
@@ -16339,7 +16345,7 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>220</v>
@@ -16383,7 +16389,7 @@
         <v>77</v>
       </c>
       <c r="S130" t="s" s="2">
-        <v>221</v>
+        <v>292</v>
       </c>
       <c r="T130" t="s" s="2">
         <v>77</v>
@@ -16451,7 +16457,7 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>225</v>
@@ -16565,7 +16571,7 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>229</v>
@@ -16677,7 +16683,7 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>232</v>
@@ -16789,7 +16795,7 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>234</v>
@@ -16901,7 +16907,7 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>237</v>
@@ -16912,7 +16918,7 @@
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G135" t="s" s="2">
         <v>87</v>
@@ -17013,7 +17019,7 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>240</v>
@@ -17125,7 +17131,7 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>244</v>
@@ -17237,7 +17243,7 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>245</v>
@@ -17351,7 +17357,7 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>246</v>
@@ -17467,7 +17473,7 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>247</v>
@@ -17579,7 +17585,7 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>250</v>
@@ -17691,7 +17697,7 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B142" t="s" s="2">
         <v>253</v>
@@ -17805,7 +17811,7 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>257</v>
@@ -17919,7 +17925,7 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>261</v>
@@ -18033,13 +18039,13 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>174</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D145" t="s" s="2">
         <v>77</v>
@@ -18064,7 +18070,7 @@
         <v>144</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M145" t="s" s="2">
         <v>177</v>
@@ -18147,7 +18153,7 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>181</v>
@@ -18259,7 +18265,7 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>182</v>
@@ -18373,7 +18379,7 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B148" t="s" s="2">
         <v>183</v>
@@ -18489,7 +18495,7 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B149" t="s" s="2">
         <v>184</v>
@@ -18601,7 +18607,7 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B150" t="s" s="2">
         <v>187</v>
@@ -18715,14 +18721,14 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>191</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
@@ -18741,13 +18747,13 @@
         <v>77</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -18816,7 +18822,7 @@
         <v>77</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>77</v>
@@ -18827,7 +18833,7 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B152" t="s" s="2">
         <v>195</v>
@@ -18939,7 +18945,7 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B153" t="s" s="2">
         <v>199</v>
@@ -19051,7 +19057,7 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>200</v>
@@ -19165,7 +19171,7 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B155" t="s" s="2">
         <v>201</v>
@@ -19281,7 +19287,7 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B156" t="s" s="2">
         <v>202</v>
@@ -19395,7 +19401,7 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B157" t="s" s="2">
         <v>208</v>
@@ -19509,7 +19515,7 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B158" t="s" s="2">
         <v>213</v>
@@ -19538,7 +19544,7 @@
         <v>144</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M158" t="s" s="2">
         <v>215</v>
@@ -19621,7 +19627,7 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B159" t="s" s="2">
         <v>217</v>
@@ -19733,7 +19739,7 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B160" t="s" s="2">
         <v>218</v>
@@ -19847,7 +19853,7 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B161" t="s" s="2">
         <v>219</v>
@@ -19963,7 +19969,7 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B162" t="s" s="2">
         <v>220</v>
@@ -20007,7 +20013,7 @@
         <v>77</v>
       </c>
       <c r="S162" t="s" s="2">
-        <v>221</v>
+        <v>412</v>
       </c>
       <c r="T162" t="s" s="2">
         <v>77</v>
@@ -20075,7 +20081,7 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B163" t="s" s="2">
         <v>225</v>
@@ -20189,7 +20195,7 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B164" t="s" s="2">
         <v>229</v>
@@ -20301,7 +20307,7 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B165" t="s" s="2">
         <v>232</v>
@@ -20413,7 +20419,7 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B166" t="s" s="2">
         <v>234</v>
@@ -20525,7 +20531,7 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B167" t="s" s="2">
         <v>237</v>
@@ -20637,7 +20643,7 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B168" t="s" s="2">
         <v>240</v>
@@ -20749,7 +20755,7 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B169" t="s" s="2">
         <v>244</v>
@@ -20861,7 +20867,7 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B170" t="s" s="2">
         <v>245</v>
@@ -20975,7 +20981,7 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B171" t="s" s="2">
         <v>246</v>
@@ -21091,7 +21097,7 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B172" t="s" s="2">
         <v>247</v>
@@ -21203,7 +21209,7 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B173" t="s" s="2">
         <v>250</v>
@@ -21315,7 +21321,7 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B174" t="s" s="2">
         <v>253</v>
@@ -21429,7 +21435,7 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B175" t="s" s="2">
         <v>257</v>
@@ -21543,7 +21549,7 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B176" t="s" s="2">
         <v>261</v>
@@ -21657,10 +21663,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -21683,19 +21689,19 @@
         <v>88</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="O177" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>77</v>
@@ -21744,7 +21750,7 @@
         <v>77</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>78</v>
